--- a/ICT_AX_공고_최근1주일.xlsx
+++ b/ICT_AX_공고_최근1주일.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,11 +533,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16712</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,11 +566,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16682</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,11 +599,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16680</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,11 +632,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16676</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,11 +665,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16675</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -718,11 +698,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16671</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -755,11 +731,7 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16668</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -769,34 +741,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AI, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,7 +774,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -816,24 +784,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -843,7 +807,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -853,24 +817,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -880,7 +840,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -890,24 +850,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
+          <t>국가유산청</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -917,34 +873,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
+          <t>대통령경호처</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -954,7 +906,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -964,24 +916,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
+          <t>산업통상부</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-04-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +939,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1001,24 +949,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
+          <t>통일부</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-23 ~ 2026-07-06</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1028,7 +972,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1038,24 +982,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
+          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-27</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-14 ~ 2026-05-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1065,7 +1005,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1075,24 +1015,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-13 ~ 2026-04-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1102,7 +1038,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1112,24 +1048,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-28</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-13 ~ 2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1139,7 +1071,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1149,24 +1081,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
+          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-27</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-09 ~ 2026-05-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1176,34 +1104,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-05-04</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-28 ~ 2026-05-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1213,34 +1137,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2027-01-30</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-05-07 ~ 2026-05-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1250,7 +1170,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1260,24 +1180,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
+          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01 ~ 2027-01-30</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-01-23 ~ 2026-02-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1287,34 +1203,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
+          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-02-12 ~ 2026-04-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1324,7 +1236,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1334,24 +1246,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-05-08</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>2026-03-27 ~ 2026-04-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1361,7 +1269,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1371,24 +1279,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>2026-03-27 ~ 2026-04-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1398,7 +1302,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1408,24 +1312,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-23 ~ 2026-05-11</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1435,7 +1335,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1445,24 +1345,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>세부사업별 상이</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,7 +1368,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1482,24 +1378,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1509,7 +1401,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1519,24 +1411,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1551,12 +1439,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 데이터</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
+          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1566,12 +1454,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-10-31</t>
+          <t>2026-04-08 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1481,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
+          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1603,12 +1491,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-15 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1513,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
+          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,12 +1528,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-15 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1555,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
+          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1677,12 +1565,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1587,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
+          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1714,12 +1602,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1629,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
+          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1751,12 +1639,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-09 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1666,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
+          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1788,12 +1676,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-11-30</t>
+          <t>2026-04-23 ~ 2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1698,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AI, 실증</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
+          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1825,12 +1713,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-23</t>
+          <t>2026-04-08 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1740,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
+          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1862,12 +1750,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-30</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1777,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
+          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1899,12 +1787,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>모집 완료시</t>
+          <t>2026-04-08 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1814,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1936,12 +1824,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-07 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1851,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1973,12 +1861,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-08 ~ 2026-05-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1888,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
+          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2010,12 +1898,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-07 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2037,7 +1925,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
+          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2047,12 +1935,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-27</t>
+          <t>2026-04-01 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2074,7 +1962,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
+          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2084,12 +1972,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2111,7 +1999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
+          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2121,12 +2009,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-30</t>
+          <t>2026-04-07 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2036,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
+          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2158,12 +2046,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-27</t>
+          <t>2026-04-07 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2073,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
+          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2195,12 +2083,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-28</t>
+          <t>2026-03-23 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2110,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
+          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2232,12 +2120,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-20 ~ 2026-04-24</t>
+          <t>세부사업별 상이</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2259,22 +2147,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
+          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-21</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2296,22 +2184,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
+          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2333,22 +2221,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
+          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-20</t>
+          <t>2026-04-10 ~ 2026-10-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2370,22 +2258,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
+          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2402,27 +2290,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
+          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2444,22 +2332,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
+          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-06</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2369,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
+          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-23</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2518,22 +2406,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
+          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-01</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2555,22 +2443,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-13 ~ 2026-11-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2587,27 +2475,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
+          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2624,27 +2512,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AI, 실증, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
+          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-14 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2666,22 +2554,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
+          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-03 ~ 2026-05-30</t>
+          <t>모집 완료시</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2703,22 +2591,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
+          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2740,22 +2628,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
+          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2777,22 +2665,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
+          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2814,22 +2702,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-10 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2851,22 +2739,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
+          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2888,22 +2776,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
+          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-10 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2925,22 +2813,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-13 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2962,22 +2850,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-14 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -2999,22 +2887,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-20 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3036,7 +2924,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3046,12 +2934,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-08 ~ 2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3073,7 +2961,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
+          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3083,12 +2971,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-04 ~ 2026-05-08</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3110,7 +2998,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3120,12 +3008,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-06 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3142,12 +3030,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3157,12 +3045,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-08-28</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3072,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3194,12 +3082,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-06-12</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3109,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3231,12 +3119,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3146,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3268,12 +3156,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3183,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3305,12 +3193,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3220,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3342,12 +3230,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3257,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3379,12 +3267,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3289,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 데이터</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3416,12 +3304,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3331,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3453,12 +3341,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-11</t>
+          <t>2026-04-03 ~ 2026-05-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3368,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3490,12 +3378,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-19</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3517,20 +3405,797 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-13 ~ 2026-04-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-04 ~ 2026-05-08</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-13 ~ 2026-04-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-06-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-13 ~ 2026-04-24</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-05-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-19</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>2026년 1차 세라믹서포터즈사업화R&amp;D지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-04-06 ~ 2026-04-19</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
         </is>

--- a/ICT_AX_공고_최근1주일.xlsx
+++ b/ICT_AX_공고_최근1주일.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
+          <t>국가과학자 test</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,21 +496,17 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16720</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,12 +516,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
+          <t>2026년도 연합학습 기반 신약개발 가속화 프로젝트 사업신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -538,27 +534,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
+          <t>2026년도 R&amp;D 매니지먼트 선진화 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -571,12 +567,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -586,12 +582,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
+          <t>2026년도 기업수요기반 1% MVP 프로젝트 사업 공동연구기관 선정 공고(연장공고)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -604,27 +600,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AI, 실증, 디지털전환</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
+          <t>2026년도 개도국기후기술실증연구 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -637,12 +633,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -652,12 +648,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
+          <t>2026년도 미래 혁신 선도형 이차전지 원천기술개발 사업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -670,12 +666,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -685,12 +681,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
+          <t>2026년도 치매의료기술연구개발사업 하반기 신규과제 공모</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -703,12 +699,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -718,12 +714,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
+          <t>차세대 재생에너지 표준화 및 인증고도화 혁신 지원 2026년 신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -736,32 +732,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년도 한국형Manufacturing-X플랫폼표준모델개발및실증(R&amp;D) 신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -769,12 +765,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -784,17 +780,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년도 한-스위스 박사(박사후)과정생 연수사업 (인력교류사업) 과제 공모</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -807,7 +803,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -817,20 +813,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>상세 접속 필요</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-2/16720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>국가유산청</t>
+          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -873,27 +873,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대통령경호처</t>
+          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>산업통상부</t>
+          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -939,27 +939,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 디지털전환</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>통일부</t>
+          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
+          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1015,17 +1015,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
+          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
+          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1081,17 +1081,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-05-08</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28 ~ 2026-05-12</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-07 ~ 2026-05-22</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1180,17 +1180,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
+          <t>국가유산청</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-23 ~ 2026-02-23</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1208,22 +1208,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
+          <t>대통령경호처</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-12 ~ 2026-04-16</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1246,17 +1246,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
+          <t>산업통상부</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
+          <t>통일부</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-09 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1434,34 +1434,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI, 데이터</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-29</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-04-28 ~ 2026-05-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1471,34 +1467,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-05-07 ~ 2026-05-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1508,7 +1500,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1518,24 +1510,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
+          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-14</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-01-23 ~ 2026-02-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1545,34 +1533,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
+          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-02-12 ~ 2026-04-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1582,34 +1566,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-03-27 ~ 2026-04-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1619,7 +1599,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1629,24 +1609,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-04-27</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>2026-03-27 ~ 2026-04-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1666,24 +1642,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-23 ~ 2026-07-06</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1693,7 +1665,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1703,24 +1675,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-27</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1730,7 +1698,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1740,24 +1708,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1767,7 +1731,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1777,24 +1741,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-28</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1809,12 +1769,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 데이터</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
+          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1824,7 +1784,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-27</t>
+          <t>2026-04-08 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1851,7 +1811,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
+          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1861,7 +1821,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-05-04</t>
+          <t>2026-04-15 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1888,7 +1848,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
+          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1898,7 +1858,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2027-01-30</t>
+          <t>2026-04-15 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1925,7 +1885,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
+          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1935,7 +1895,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01 ~ 2027-01-30</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1957,12 +1917,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
+          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1972,7 +1932,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-11</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1999,7 +1959,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
+          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2009,12 +1969,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-05-08</t>
+          <t>2026-04-09 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2036,7 +1996,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
+          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2046,12 +2006,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-23</t>
+          <t>2026-04-23 ~ 2026-07-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2033,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
+          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2083,12 +2043,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23 ~ 2026-05-11</t>
+          <t>2026-04-08 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2070,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
+          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2120,12 +2080,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>세부사업별 상이</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2107,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
+          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2157,12 +2117,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>2026-04-08 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2144,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
+          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2194,12 +2154,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>2026-04-07 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2181,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
+          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2231,12 +2191,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-10-31</t>
+          <t>2026-04-08 ~ 2026-05-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2218,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
+          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2268,12 +2228,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-07 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2250,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
+          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2305,12 +2265,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-01 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2292,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
+          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2342,12 +2302,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2329,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
+          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2379,7 +2339,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-07 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2406,7 +2366,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
+          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2416,7 +2376,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-07 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2443,7 +2403,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
+          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2453,7 +2413,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-11-30</t>
+          <t>2026-03-23 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2475,12 +2435,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AI, 실증</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
+          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2490,7 +2450,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-23</t>
+          <t>세부사업별 상이</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2517,7 +2477,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
+          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2527,7 +2487,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-30</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2554,7 +2514,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
+          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2564,12 +2524,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>모집 완료시</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2551,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2601,12 +2561,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-10 ~ 2026-10-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2588,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2643,7 +2603,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2620,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
+          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2675,12 +2635,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2662,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
+          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2712,12 +2672,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-27</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2699,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
+          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2749,12 +2709,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2736,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
+          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2786,12 +2746,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-30</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2773,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2823,12 +2783,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-27</t>
+          <t>2026-04-13 ~ 2026-11-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2805,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
+          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2860,12 +2820,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-28</t>
+          <t>2026-04-10 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2847,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
+          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2897,12 +2857,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-20 ~ 2026-04-24</t>
+          <t>2026-04-14 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2924,17 +2884,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
+          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-21</t>
+          <t>모집 완료시</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2961,17 +2921,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
+          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2998,17 +2958,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
+          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-20</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3035,17 +2995,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
+          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3072,17 +3032,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
+          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3109,22 +3069,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
+          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-06</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3106,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
+          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-23</t>
+          <t>2026-04-10 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3183,22 +3143,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
+          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-01</t>
+          <t>2026-04-13 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3220,22 +3180,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
+          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-14 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3257,22 +3217,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
+          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-20 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3249,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI, 실증, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
+          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3304,12 +3264,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-08 ~ 2026-04-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3291,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
+          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3341,12 +3301,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-03 ~ 2026-05-30</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3328,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
+          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3378,12 +3338,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3365,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
+          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3415,12 +3375,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3402,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
+          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3457,7 +3417,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3439,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3489,7 +3449,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3516,7 +3476,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
+          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3526,7 +3486,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3553,7 +3513,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
+          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3563,7 +3523,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3590,7 +3550,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3600,7 +3560,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3627,7 +3587,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3637,7 +3597,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3659,12 +3619,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 데이터</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3674,12 +3634,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3661,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3711,12 +3671,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-03 ~ 2026-05-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3698,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
+          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3748,12 +3708,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-04 ~ 2026-05-08</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3735,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3785,12 +3745,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3767,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3822,12 +3782,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-08-28</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3809,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3859,12 +3819,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-06-12</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3846,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3896,12 +3856,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3883,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3933,12 +3893,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3920,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3970,12 +3930,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3957,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4012,7 +3972,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4034,7 +3994,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4044,7 +4004,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4071,7 +4031,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4081,7 +4041,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4108,7 +4068,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4118,7 +4078,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-11</t>
+          <t>2026-05-04 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4145,7 +4105,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4155,7 +4115,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-19</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4177,25 +4137,395 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-08-28</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-06-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>예산 소진시까지</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-13 ~ 2026-04-24</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-05-11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-19</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>2026년 1차 세라믹서포터즈사업화R&amp;D지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>2026-04-06 ~ 2026-04-19</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
         </is>

--- a/ICT_AX_공고_최근1주일.xlsx
+++ b/ICT_AX_공고_최근1주일.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,12 +798,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>기업마당</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
+          <t>2026년 하반기 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 시행계획 공고</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -823,24 +823,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>상세 접속 필요</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16720</t>
-        </is>
-      </c>
+          <t>2026-04-23 ~ 2026-07-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>기업마당</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -850,17 +846,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
+          <t>2026년 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>상세 접속 필요</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -878,17 +874,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
+          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -896,7 +892,11 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-2/16720</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
+          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI, 실증, 디지털전환</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
+          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
+          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 디지털전환</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
+          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
+          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국가유산청</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>대통령경호처</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>산업통상부</t>
+          <t>국가유산청</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>통일부</t>
+          <t>대통령경호처</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
+          <t>산업통상부</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
+          <t>통일부</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
+          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-05-08</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1439,22 +1439,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-28 ~ 2026-05-12</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1472,22 +1472,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
+          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-07 ~ 2026-05-22</t>
+          <t>2026-04-09 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1505,22 +1505,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-01-23 ~ 2026-02-23</t>
+          <t>2026-04-28 ~ 2026-05-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1543,17 +1543,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-12 ~ 2026-04-16</t>
+          <t>2026-05-07 ~ 2026-05-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
+          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>2026-01-23 ~ 2026-02-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1604,22 +1604,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
+          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>2026-02-12 ~ 2026-04-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1642,17 +1642,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1764,34 +1764,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AI, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1801,7 +1797,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1811,24 +1807,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1843,12 +1835,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 데이터</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
+          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1858,7 +1850,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-14</t>
+          <t>2026-04-08 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1885,7 +1877,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
+          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1895,7 +1887,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
+          <t>2026-04-15 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1917,12 +1909,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
+          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1932,7 +1924,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
+          <t>2026-04-15 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1959,7 +1951,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
+          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1969,7 +1961,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-04-27</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1991,12 +1983,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
+          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2006,7 +1998,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-23 ~ 2026-07-06</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2033,7 +2025,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
+          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2043,7 +2035,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-27</t>
+          <t>2026-04-09 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2070,7 +2062,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
+          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2080,7 +2072,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-23 ~ 2026-07-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2107,7 +2099,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
+          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2117,7 +2109,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-28</t>
+          <t>2026-04-08 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2144,7 +2136,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
+          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2154,7 +2146,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-27</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2181,7 +2173,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
+          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2191,7 +2183,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-05-04</t>
+          <t>2026-04-08 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2218,7 +2210,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
+          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2228,7 +2220,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2027-01-30</t>
+          <t>2026-04-07 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2255,7 +2247,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
+          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2265,7 +2257,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-01 ~ 2027-01-30</t>
+          <t>2026-04-08 ~ 2026-05-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2292,7 +2284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
+          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2302,7 +2294,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-11</t>
+          <t>2026-04-07 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2329,7 +2321,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
+          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2339,12 +2331,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-05-08</t>
+          <t>2026-04-01 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2358,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
+          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2376,12 +2368,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-23</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2395,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
+          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2413,7 +2405,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23 ~ 2026-05-11</t>
+          <t>2026-04-07 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
+          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2450,7 +2442,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>세부사업별 상이</t>
+          <t>2026-04-07 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2477,7 +2469,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
+          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2487,7 +2479,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>2026-03-23 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2514,7 +2506,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
+          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2524,7 +2516,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>세부사업별 상이</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2551,7 +2543,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
+          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2561,7 +2553,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-10-31</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2588,7 +2580,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
+          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2598,7 +2590,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2620,12 +2612,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
+          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2635,7 +2627,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-10 ~ 2026-10-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2662,7 +2654,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
+          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2672,7 +2664,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2694,12 +2686,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
+          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2709,7 +2701,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2736,7 +2728,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
+          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2746,7 +2738,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2773,7 +2765,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
+          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2783,7 +2775,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-11-30</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2805,12 +2797,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI, 실증</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
+          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2820,7 +2812,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-23</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2847,7 +2839,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2857,7 +2849,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-30</t>
+          <t>2026-04-13 ~ 2026-11-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2879,12 +2871,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
+          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2894,12 +2886,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>모집 완료시</t>
+          <t>2026-04-10 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2913,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2931,12 +2923,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-14 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2950,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2968,7 +2960,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>모집 완료시</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2995,7 +2987,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
+          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3005,7 +2997,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3032,7 +3024,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
+          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3042,7 +3034,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-27</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3069,7 +3061,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
+          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3079,7 +3071,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3106,7 +3098,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
+          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3116,7 +3108,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-30</t>
+          <t>2026-04-10 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3143,7 +3135,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
+          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3153,7 +3145,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-27</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3180,7 +3172,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
+          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3190,7 +3182,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-28</t>
+          <t>2026-04-10 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3217,7 +3209,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
+          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3227,7 +3219,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-20 ~ 2026-04-24</t>
+          <t>2026-04-13 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3254,17 +3246,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
+          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-21</t>
+          <t>2026-04-14 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3291,17 +3283,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
+          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-20 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3328,7 +3320,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
+          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3338,7 +3330,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-20</t>
+          <t>2026-04-08 ~ 2026-04-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3365,7 +3357,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
+          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3375,7 +3367,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3402,7 +3394,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
+          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3412,7 +3404,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3439,7 +3431,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
+          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3449,12 +3441,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-06</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3468,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
+          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3486,12 +3478,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-23</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3505,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
+          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3523,7 +3515,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-01</t>
+          <t>2026-04-06 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3550,7 +3542,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
+          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3560,7 +3552,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
+          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3597,7 +3589,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-05-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3619,12 +3611,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AI, 실증, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
+          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3634,7 +3626,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3661,7 +3653,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
+          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3671,7 +3663,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-03 ~ 2026-05-30</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3693,12 +3685,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 데이터</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
+          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3708,7 +3700,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3735,7 +3727,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
+          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3745,7 +3737,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-03 ~ 2026-05-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3772,7 +3764,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
+          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3809,7 +3801,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3819,7 +3811,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3846,7 +3838,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
+          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3883,7 +3875,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
+          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3920,7 +3912,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3957,7 +3949,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3994,7 +3986,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4004,12 +3996,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4023,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4041,12 +4033,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4060,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
+          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4078,7 +4070,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-04 ~ 2026-05-08</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4105,7 +4097,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4115,7 +4107,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4137,12 +4129,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4152,7 +4144,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-08-28</t>
+          <t>2026-05-04 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4179,7 +4171,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4189,7 +4181,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-06-12</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4211,12 +4203,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4226,7 +4218,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-08-28</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4253,7 +4245,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4263,7 +4255,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-06-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4290,7 +4282,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4300,7 +4292,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4327,7 +4319,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4337,7 +4329,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4364,7 +4356,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4374,7 +4366,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-13 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4401,7 +4393,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4411,7 +4403,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4438,7 +4430,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4448,7 +4440,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-11</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4475,7 +4467,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4485,7 +4477,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-19</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4512,20 +4504,94 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-05-11</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-19</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>2026년 1차 세라믹서포터즈사업화R&amp;D지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>2026-04-06 ~ 2026-04-19</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
         </is>

--- a/ICT_AX_공고_최근1주일.xlsx
+++ b/ICT_AX_공고_최근1주일.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +803,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026년 하반기 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 시행계획 공고</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-23 ~ 2026-07-06</t>
+          <t>2026-04-14 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026년 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
+          <t>「NST 출연연 패널조사 기획 및 조사·분석 연구」정책연구과제 공고</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-11</t>
+          <t>2026-04-14 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -864,12 +864,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>기업마당</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
+          <t>2026년 하반기 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 시행계획 공고</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -889,24 +889,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>상세 접속 필요</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-2/16720</t>
-        </is>
-      </c>
+          <t>2026-04-23 ~ 2026-07-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>기업마당</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,17 +912,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
+          <t>2026년 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>상세 접속 필요</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -934,32 +930,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>기업마당</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
+          <t>2026년 IP 라이선싱 빌드업 참가기업(중소IP사) 모집 공고</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>상세 접속 필요</t>
+          <t>2026-04-06 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -982,12 +978,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
+          <t>싱가포르IT지원센터 2026년 상반기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -995,7 +991,11 @@
           <t>상세 접속 필요</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-2/16720</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI, 실증, 디지털전환</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
+          <t>2026년도 호치민IT지원센터 공간 효율화를 위한 인테리어 용역 입찰 공고</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
+          <t>2026년 1차 ICT 비즈니스 파트너십(아세안) 참가기업 모집</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
+          <t>하노이 IT지원센터 ‘26년 상반기 연간/단기 입주기업 모집 공고</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 디지털전환</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
+          <t>2026년 AI·디지털전환 혁신기업 해외실증 지원 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년 DNA 융합 제품·서비스 해외진출 지원 사업  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>[재공고]2026년 소프트웨어 인재키움 사업 수행지역 및 기관 선정 공고</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTIS</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>「첨단 GPU 활용 지원 사업」사용자 수시 모집 공고</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>상세 접속 필요</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>국가유산청</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>대통령경호처</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>산업통상부</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>통일부</t>
+          <t>국가유산청</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
+          <t>대통령경호처</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
+          <t>산업통상부</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
+          <t>통일부</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1477,17 +1477,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
+          <t>2026년 산학연 연계 중소벤처 RBD 지원사업(STEP 4)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-05-08</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1505,22 +1505,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-28 ~ 2026-05-12</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1538,22 +1538,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모(재공고)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-07 ~ 2026-05-22</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
+          <t>2026년 KISTEP 기본사업 위탁연구과제 공모(과학기술 논문성과 분석연구(2011-2025))</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-23 ~ 2026-02-23</t>
+          <t>2026-04-09 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1609,17 +1609,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(중앙거점) 신규과제 공모</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-12 ~ 2026-04-16</t>
+          <t>2026-04-28 ~ 2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
+          <t>2026년 AI 기반 대학 과학기술 혁신사업(AI4ST) 신규과제 공모</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>2026-05-07 ~ 2026-05-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
+          <t>2026년도 Net-zero구현초격차태양전지개발 사업 신규과제 공모</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-10</t>
+          <t>2026-01-23 ~ 2026-02-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1703,22 +1703,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>해외우수과학자유치사업 (Brain Pool / Brain Pool+) 2026년도 신규과제 공고</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-02-12 ~ 2026-04-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 위탁과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>더보기</t>
+          <t>2026년도 한국철도기술연구원 기본사업 신규 공동과제 수행기관 공모</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-03-27 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1830,34 +1830,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AI, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1867,7 +1863,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1877,24 +1873,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
+          <t>더보기</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>기업마당</t>
+          <t>NTIS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1914,24 +1906,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-14</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
-        </is>
-      </c>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1946,12 +1934,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 데이터</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
+          <t>[전남] 2026년 AIㆍ데이터 스타트업 성장 지원사업 공고</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1961,7 +1949,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
+          <t>2026-04-08 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1983,12 +1971,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
+          <t>2026년 소공인 인프라시설 고도화 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1998,7 +1986,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-05-06</t>
+          <t>2026-04-15 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2025,7 +2013,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
+          <t>2026년 중소기업 혁신 유공 포상 후보자 모집 공고</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2035,7 +2023,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-09 ~ 2026-04-27</t>
+          <t>2026-04-15 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2062,7 +2050,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
+          <t>2026년 1차 일반 물류바우처 사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2072,7 +2060,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-23 ~ 2026-07-06</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2094,12 +2082,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
+          <t>2026년 2차 수출지원기반활용사업 참여기업 모집 공고(중소벤처기업부 소관 수출바우처사업)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-27</t>
+          <t>2026-04-17 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2136,7 +2124,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
+          <t>2026년 글로벌스케일업캠퍼스 인천 유니브-엑스(Univ. X) 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2146,7 +2134,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-09 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2173,7 +2161,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
+          <t>2026년 중소기업기술혁신개발사업 유망기술개발(구조혁신R&amp;D) 하반기 시행계획 공고</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2183,7 +2171,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-28</t>
+          <t>2026-04-23 ~ 2026-07-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2210,7 +2198,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
+          <t>[전남] 2026년 가정간편식 제품 개발 지원사업 지원기업 모집 공고</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2220,7 +2208,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-27</t>
+          <t>2026-04-08 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2247,7 +2235,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
+          <t>2026년 아산시 단체관광객 유치 인센티브 지원계획 공고</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2257,7 +2245,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-05-04</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2284,7 +2272,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
+          <t>2026년 전북 글로벌게임센터 고도화 게임 제작지원사업 공고</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2294,7 +2282,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2027-01-30</t>
+          <t>2026-04-08 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2321,7 +2309,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
+          <t>2026년 K-뷰티ㆍ헬스케어 현지진출 프로그램  참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2331,7 +2319,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-01 ~ 2027-01-30</t>
+          <t>2026-04-07 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2358,7 +2346,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
+          <t>2026년 혁신 프리미어 1000 녹색산업 우수기업 모집 공고</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2368,7 +2356,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-05-11</t>
+          <t>2026-04-08 ~ 2026-05-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2395,7 +2383,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
+          <t>[강원] 춘천시 2026년 생계형 1인 자영업자 사회보험료 지원 공고</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2405,12 +2393,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-05-08</t>
+          <t>2026-04-07 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2420,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
+          <t>[강원] 춘천시 2026년 사회보험료(10인 미만) 지원 공고</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2442,12 +2430,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-07 ~ 2026-04-23</t>
+          <t>2026-04-01 ~ 2027-01-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2457,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
+          <t>2026년도 전통시장 및 상점가 활성화 유공 포상 계획 공고</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2479,12 +2467,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-23 ~ 2026-05-11</t>
+          <t>2026-04-15 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=1</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2494,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
+          <t>[충남] 아산시 2026년 3차 소규모사업장 대기방지시설 사물인터넷(IoT) 설치 지원사업 시행 계획 공고</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2516,7 +2504,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>세부사업별 상이</t>
+          <t>2026-04-07 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2543,7 +2531,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
+          <t>[울산] 2026년 베트남 종합 무역사절단 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2553,7 +2541,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>2026-04-07 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2580,7 +2568,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
+          <t>2026년 북미 진출 GATE 프로그램 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2590,7 +2578,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>선착순 접수</t>
+          <t>2026-03-23 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2617,7 +2605,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
+          <t>[경기] 포천시 2026년 지역소공인육성사업 소공인특화지원센터 지원사업 공고</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2627,7 +2615,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-10-31</t>
+          <t>세부사업별 상이</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2654,7 +2642,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
+          <t>[울산] 2026년 소상공인 재기지원자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2664,7 +2652,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2686,12 +2674,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>수출</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
+          <t>[울산] 2026년 2차 소상공인 경영안정자금 긴급 융자 지원계획 공고</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2701,7 +2689,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>선착순 접수</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2728,7 +2716,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
+          <t>[전북] 2026년 전북특별자치도소상공인희망센터 컨설팅 지원 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2738,7 +2726,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-10-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2765,7 +2753,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
+          <t>[강원] 춘천시 2026년 1차 지식재산 국내분쟁 비용지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2797,12 +2785,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수출</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
+          <t>2026년 중동 상황 대응 긴급 수출물류비 사업 대상 모집 공고</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2839,7 +2827,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
+          <t>[강원] 2026년 지역혁신클러스터육성(비R&amp;D) 기업지원 프로그램 모집 공고</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2849,7 +2837,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-11-30</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2871,12 +2859,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AI, 실증</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
+          <t>[경북] 영천시 2026년 중소기업 고부가가치 전환육성 지원사업 공고</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2886,7 +2874,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-23</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2913,7 +2901,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
+          <t>[경북] 영천시 2026년 영천기업 연구시설장비 바우처 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2923,7 +2911,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-30</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2950,7 +2938,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
+          <t>2026년 디지털커머스 전문기관(소담스퀘어강원) 소상공인 모집 공고</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2960,12 +2948,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>모집 완료시</t>
+          <t>2026-04-13 ~ 2026-11-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2970,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[호남권] 2026년 AI융합 지능형 농업생태계 구축사업 AI솔루션 실증 지원사업 통합 모집 공고</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2997,12 +2985,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-10 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3012,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
+          <t>[서울] 2026년 지역수요 맞춤형 R&amp;D기획 지원사업 공고</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3034,12 +3022,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-05-11</t>
+          <t>2026-04-14 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=2</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3049,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
+          <t>[경북] 2026년 경북세일페스타 온라인 기획전 참여업체 모집 공고</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3071,7 +3059,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>모집 완료시</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3098,7 +3086,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
+          <t>[강원] 원주시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3108,7 +3096,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-27</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3135,7 +3123,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
+          <t>[강원] 강릉시 2026년 1차 중소기업 지식재산 국내 분쟁 지원 사업 모집 공고</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3145,7 +3133,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-14</t>
+          <t>2026-04-10 ~ 2026-05-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3172,7 +3160,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
+          <t>2026년 2분기 자랑스러운 중소기업인 접수 공고</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3182,7 +3170,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3209,7 +3197,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
+          <t>2026년 생활용 섬유제품 제조역량강화사업 지원대상기업 모집 통합 공고</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3219,7 +3207,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-27</t>
+          <t>2026-04-10 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3246,7 +3234,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
+          <t>[경북] 2026년 산학연 연계 중소벤처 R&amp;BD 지원사업(산학연 연계 핵심 R&amp;D STEP 4) 시행계획 공고</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3256,7 +3244,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-28</t>
+          <t>2026-04-14 ~ 2026-05-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3283,7 +3271,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
+          <t>[울산] 2026년 U-RISE 스타트업 캠퍼스 창업팀 모집 공고</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3293,7 +3281,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-20 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3320,17 +3308,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
+          <t>[경기] 2026년 1차 경기스타트업플랫폼 투자연계 지원 프로그램 온라인 밋업위크 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08 ~ 2026-04-21</t>
+          <t>2026-04-13 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3357,17 +3345,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
+          <t>[경기] 성남시 2026년 독일 뒤셀도르프 의료기기전시회(MEDICA 2026) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-14 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3394,17 +3382,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
+          <t>[경북] 2026년 2차 지역혁신 프로젝트 혁신창업ㆍ데스벨리 지원 공고</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-20</t>
+          <t>2026-04-20 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3431,7 +3419,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
+          <t>[경북] 2026년 2차 중소기업 공공조달시장 진출 지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3441,7 +3429,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-08 ~ 2026-04-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3468,7 +3456,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
+          <t>[경북] 소공인 스케일업 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3505,7 +3493,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
+          <t>[경남] 2026년 2차 우주항공분야 타깃마케팅(영국 2026 판보로에어쇼) 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3515,12 +3503,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-06</t>
+          <t>2026-04-06 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3530,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
+          <t>[광주] 2026년 해외 세일즈출장 및 바이어초청 지원사업 참가업체 모집 공고</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3552,12 +3540,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-23</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3567,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
+          <t>[강원] 동해시 2026년 자유무역지역 역량강화 기업지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3589,12 +3577,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-01</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=3</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3604,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
+          <t>2026년 플라스틱 순환경제 해외진출 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3626,7 +3614,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3653,7 +3641,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
+          <t>[광주] 2026년 융ㆍ복합 가전산업 기업 브랜드 강화 지원 사업 참여 기업 모집 공고(지역주도형 일자리 지원사업)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3663,7 +3651,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-10 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3685,12 +3673,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AI, 실증, 데이터</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
+          <t>[경기] 화성시 2026년 소상공인 클린케어 지원사업 시행 공고</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3700,7 +3688,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-05-08</t>
+          <t>2026-04-06 ~ 2026-05-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3727,7 +3715,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
+          <t>[경기] 2026년 경기가족친화 일하기 좋은 기업 인증 지원사업 공고</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3737,7 +3725,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-03 ~ 2026-05-30</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3764,7 +3752,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
+          <t>[광주] 2026년 중소사업장 가족친화경영지원사업 모집 공고</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3774,7 +3762,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-10 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3796,12 +3784,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI, 실증, 데이터</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
+          <t>[경기] 2026년 산업데이터 표준 기반 AI솔루션 실증지원 수요기업 모집 공고(산업데이터 표준 확산 기반 구축 사업)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3811,7 +3799,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-06 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3838,7 +3826,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
+          <t>[대전] 2026년 해외통상사무소 주관 해외바이어 초청 비즈니스 상담회 공고</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3848,7 +3836,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-03 ~ 2026-05-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3875,7 +3863,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[경북] 소공인 환경개선 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3885,7 +3873,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3912,7 +3900,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
+          <t>2026년 일본 도쿄 추계 IT 주간 전시회(Japan IT Week Autumn) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3922,7 +3910,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3949,7 +3937,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
+          <t>[경북] 소공인 온라인 콘텐츠 마케팅 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3959,7 +3947,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3986,7 +3974,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[대전] 2026년 디자인 라이선스 지원사업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4023,7 +4011,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>2026년 홍콩 주얼리&amp;젬월드 전시회(Jewellery &amp; Gem WORLD Hong Kong) 한국관 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4033,7 +4021,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4060,7 +4048,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4070,12 +4058,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-20</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4085,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
+          <t>[대전] 2026년 ESG 경영환경 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4107,12 +4095,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4122,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
+          <t>[대전] 2026년 청년ㆍ인쇄 협업 프로젝트 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4144,12 +4132,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-04 ~ 2026-05-08</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=4</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4159,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
+          <t>[부산] 2026년 지산학 스케일업 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4203,12 +4191,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
+          <t>[대전] 2026년 컨설팅 지원사업 참여기업 모집 공고(대전인쇄소공인특화지원센터)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4218,7 +4206,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-08-28</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4245,7 +4233,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
+          <t>[전북] 2026년 기술닥터 프로그램 참여기업 지원 모집 공고</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4255,7 +4243,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-06-12</t>
+          <t>2026-05-04 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4282,7 +4270,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
+          <t>[부산] 2026년 1차 지산학 기술도입 지원사업 참여기업 모집 공고(지산학 연결중개 촉진 지원사업)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4292,7 +4280,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-13 ~ 2026-04-20</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4314,12 +4302,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
+          <t>[전북] ICT이노베이션스퀘어 확산사업 기업협력프로젝트 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4329,7 +4317,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>예산 소진시까지</t>
+          <t>2026-04-06 ~ 2026-08-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
+          <t>2026년 글로벌기업산업기술연계R&amp;D 사업 신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4366,7 +4354,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-06 ~ 2026-06-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4393,7 +4381,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
+          <t>[충북] 2026년 천연물 사업 다각화 지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4403,7 +4391,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>2026-04-06 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4430,7 +4418,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
+          <t>2026년 통상변화대응지원사업 참여기업 모집 공고</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4440,7 +4428,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-17</t>
+          <t>예산 소진시까지</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4467,7 +4455,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+          <t>[제주] 2026년 제주관광 콘텐츠 프로젝트 지원사업 모집 공고(지역산업맞춤형 일자리지원 사업)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4477,7 +4465,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-30</t>
+          <t>2026-04-13 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4504,7 +4492,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+          <t>[전북] 2026년 국내박람회 개별 참가 지원 참여기업 모집 공고(전북특별자치도 우수상품 판로 개척 지원)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4514,7 +4502,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-05-11</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4541,7 +4529,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+          <t>[세종] 2026년 제품 공인인증ㆍ시험비 지원사업 참여 스타트업 모집 공고(개발완성수준(TRL) 승격 지원사업)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4551,7 +4539,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-06 ~ 2026-04-19</t>
+          <t>2026-04-06 ~ 2026-04-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4578,20 +4566,131 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>[충북] 2026년 천연물 신제품 개발 및 시제품 제작 지원 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026년 초격차 스타트업 프로젝트 모두의 챌린지 팹리스 참여기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-05-11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026년 우주ㆍ항공ㆍ방산용 에너지 세라믹소재 개발 지원사업 기업모집 공고</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-06 ~ 2026-04-19</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>기업마당</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>2026년 1차 세라믹서포터즈사업화R&amp;D지원사업 수혜기업 모집 공고</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>2026-04-06 ~ 2026-04-19</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.bizinfo.go.kr/sii/siia/selectSIIA200View.do?rows=15&amp;cpage=5</t>
         </is>
